--- a/artfynd/A 1182-2022 artfynd.xlsx
+++ b/artfynd/A 1182-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1182-2022 artfynd.xlsx
+++ b/artfynd/A 1182-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88725</v>
+        <v>88712</v>
       </c>
       <c r="B2" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,14 +706,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Acksjön, V om Djupdal (delomr 2), Vstm</t>
+          <t>Acksjön, Slåttermossen, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591879.904404453</v>
+        <v>591982</v>
       </c>
       <c r="R2" t="n">
-        <v>6665438.245678308</v>
+        <v>6665317</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2007-07-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2007-11-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>88724</v>
+        <v>88713</v>
       </c>
       <c r="B3" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,14 +807,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Acksjön, V om Djupdal (delomr 2), Vstm</t>
+          <t>Acksjön, V om Slåttermossarna (delomr 2), Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591927.5909255192</v>
+        <v>591889</v>
       </c>
       <c r="R3" t="n">
-        <v>6665428.966884629</v>
+        <v>6665272</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +844,9 @@
           <t>2007-07-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2007-11-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>88902</v>
+        <v>88714</v>
       </c>
       <c r="B4" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -943,14 +908,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Acksjön, V om Djupdal (delomr 2), Vstm</t>
+          <t>Acksjön, V om Slåttermossarna (delomr 2), Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591903.7789384725</v>
+        <v>591816</v>
       </c>
       <c r="R4" t="n">
-        <v>6665442.333957224</v>
+        <v>6665294</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,19 +945,9 @@
           <t>2007-07-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2007-11-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>88713</v>
+        <v>88724</v>
       </c>
       <c r="B5" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1059,14 +1009,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Acksjön, V om Slåttermossarna (delomr 2), Vstm</t>
+          <t>Acksjön, V om Djupdal (delomr 2), Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591888.5503119795</v>
+        <v>591928</v>
       </c>
       <c r="R5" t="n">
-        <v>6665272.39667388</v>
+        <v>6665429</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,19 +1046,9 @@
           <t>2007-07-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2007-11-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,50 +1079,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113379</v>
+        <v>88725</v>
       </c>
       <c r="B6" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>210</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Acksjön, V om Slåttermossarna (delomr 2), Vstm</t>
+          <t>Acksjön, V om Djupdal (delomr 2), Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591883.9321687515</v>
+        <v>591880</v>
       </c>
       <c r="R6" t="n">
-        <v>6665257.319902239</v>
+        <v>6665438</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,19 +1147,9 @@
           <t>2007-07-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2007-11-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,50 +1180,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4886523</v>
+        <v>88902</v>
       </c>
       <c r="B7" t="n">
-        <v>101323</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222395</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Acksjön, V om Slåttermossarna (delomr 2), Vstm</t>
+          <t>Acksjön, V om Djupdal (delomr 2), Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591933.3691073956</v>
+        <v>591904</v>
       </c>
       <c r="R7" t="n">
-        <v>6665397.694252266</v>
+        <v>6665442</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1328,19 +1248,9 @@
           <t>2007-07-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2007-11-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,50 +1281,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>441271</v>
+        <v>113379</v>
       </c>
       <c r="B8" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>210</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Acksjön, Vstm</t>
+          <t>Acksjön, V om Slåttermossarna (delomr 2), Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591856.8890766423</v>
+        <v>591884</v>
       </c>
       <c r="R8" t="n">
-        <v>6665359.874399644</v>
+        <v>6665257</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1444,19 +1349,9 @@
           <t>2007-07-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2007-11-30</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,53 +1382,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>6989845</v>
+        <v>113380</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Boda, Vstm</t>
+          <t>Acksjön, V om Djupdal (delomr 1), Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>591948.7697500092</v>
+        <v>591958</v>
       </c>
       <c r="R9" t="n">
-        <v>6665480.861404434</v>
+        <v>6665441</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1557,22 +1447,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2013-06-22</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-07-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2013-10-01</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-11-30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,24 +1463,834 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>113381</v>
+      </c>
+      <c r="B10" t="n">
+        <v>96554</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>210</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Acksjön, V om Slåttermossarna (delomr 2), Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>591751</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6665400</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2007-07-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2007-11-30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>441271</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Acksjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>591857</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6665360</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2007-07-01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2007-11-30</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>441272</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Acksjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>591842</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6665279</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2007-07-01</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2007-11-30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6989850</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Boda, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>591945</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6665389</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2013-06-22</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2013-10-01</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
           <t>Mårten Berglind</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>Mårten Berglind</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6989845</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Boda, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>591949</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6665481</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2013-06-22</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2013-10-01</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Mårten Berglind</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Mårten Berglind</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6989846</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Boda, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>591781</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6665441</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2013-06-22</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2013-10-01</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Mårten Berglind</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Mårten Berglind</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>4886520</v>
+      </c>
+      <c r="B16" t="n">
+        <v>104253</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222395</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dvärghäxört</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Circaea alpina</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Acksjön, V om Slåttermossarna (delomr 2), Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>591838</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6665254</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2007-07-01</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2007-11-30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>4886523</v>
+      </c>
+      <c r="B17" t="n">
+        <v>104253</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222395</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dvärghäxört</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Circaea alpina</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Acksjön, V om Slåttermossarna (delomr 2), Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>591933</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6665398</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2007-07-01</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2007-11-30</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1182-2022 artfynd.xlsx
+++ b/artfynd/A 1182-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88712</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88713</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88714</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88724</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88725</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88902</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113379</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113380</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113381</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
           <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/441271</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
           <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/441272</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1885,6 +1945,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6989850</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1987,6 +2052,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6989845</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2089,6 +2159,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6989846</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2190,6 +2265,11 @@
           <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4886520</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2291,8 +2371,31 @@
           <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4886523</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>